--- a/cet4/result/51_艺术女神_创作女王的传奇路/51_艺术女神_创作女王的传奇路_学习版.xlsx
+++ b/cet4/result/51_艺术女神_创作女王的传奇路/51_艺术女神_创作女王的传奇路_学习版.xlsx
@@ -397,871 +397,731 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D51"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>bed</v>
       </c>
       <c r="B2" t="str">
-        <v>bed</v>
+        <v>/bed/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D2" t="str">
         <v>床</v>
       </c>
-      <c r="D2" t="str">
-        <v>bed(床)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>lately</v>
       </c>
       <c r="B3" t="str">
-        <v>lately</v>
+        <v>/ˈleɪtli/</v>
       </c>
       <c r="C3" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D3" t="str">
         <v>近来</v>
       </c>
-      <c r="D3" t="str">
-        <v>lately(近来)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>river</v>
       </c>
       <c r="B4" t="str">
-        <v>river</v>
+        <v>/ˈrɪvər/</v>
       </c>
       <c r="C4" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>河流</v>
       </c>
-      <c r="D4" t="str">
-        <v>river(河流)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>sweet</v>
       </c>
       <c r="B5" t="str">
-        <v>sweet</v>
+        <v>/swiːt/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D5" t="str">
         <v>甜的</v>
       </c>
-      <c r="D5" t="str">
-        <v>sweet(甜的)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>bureau</v>
       </c>
       <c r="B6" t="str">
-        <v>bureau</v>
+        <v>/ˈbjʊroʊ/</v>
       </c>
       <c r="C6" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>局</v>
       </c>
-      <c r="D6" t="str">
-        <v>bureau(局)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>project</v>
       </c>
       <c r="B7" t="str">
-        <v>project</v>
+        <v>/ˈprɑːdʒekt/</v>
       </c>
       <c r="C7" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D7" t="str">
         <v>项目</v>
       </c>
-      <c r="D7" t="str">
-        <v>project(项目)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>Africa</v>
       </c>
       <c r="B8" t="str">
-        <v>Africa</v>
+        <v>/ˈæfrɪkə/</v>
       </c>
       <c r="C8" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>非洲</v>
       </c>
-      <c r="D8" t="str">
-        <v>Africa(非洲)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>Japan</v>
       </c>
       <c r="B9" t="str">
-        <v>Japan</v>
+        <v>/dʒəˈpæn/</v>
       </c>
       <c r="C9" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D9" t="str">
         <v>日本</v>
       </c>
-      <c r="D9" t="str">
-        <v>Japan(日本)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>although</v>
       </c>
       <c r="B10" t="str">
-        <v>although</v>
+        <v>/ɔːlˈðoʊ/</v>
       </c>
       <c r="C10" t="str">
+        <v>conj.</v>
+      </c>
+      <c r="D10" t="str">
         <v>虽然</v>
       </c>
-      <c r="D10" t="str">
-        <v>although(虽然)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>frog</v>
       </c>
       <c r="B11" t="str">
-        <v>Africa</v>
+        <v>/frɑːɡ/</v>
       </c>
       <c r="C11" t="str">
-        <v>非洲</v>
+        <v>n./vi.</v>
       </c>
       <c r="D11" t="str">
-        <v>Africa(非洲)📢</v>
+        <v>青蛙</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>vase</v>
       </c>
       <c r="B12" t="str">
-        <v>frog</v>
+        <v>/veɪs,veɪz/</v>
       </c>
       <c r="C12" t="str">
-        <v>青蛙</v>
+        <v>n.</v>
       </c>
       <c r="D12" t="str">
-        <v>frog(青蛙)📢</v>
+        <v>花瓶</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>sixty</v>
       </c>
       <c r="B13" t="str">
-        <v>vase</v>
+        <v>/ˈsɪksti/</v>
       </c>
       <c r="C13" t="str">
-        <v>花瓶</v>
+        <v>num.</v>
       </c>
       <c r="D13" t="str">
-        <v>vase(花瓶)📢</v>
+        <v>六十</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>courage</v>
       </c>
       <c r="B14" t="str">
-        <v>sixty</v>
+        <v>/ˈkɜːrɪdʒ/</v>
       </c>
       <c r="C14" t="str">
-        <v>六十</v>
+        <v>n.</v>
       </c>
       <c r="D14" t="str">
-        <v>sixty(六十)📢</v>
+        <v>勇气</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>man</v>
       </c>
       <c r="B15" t="str">
-        <v>courage</v>
+        <v>/mæn/</v>
       </c>
       <c r="C15" t="str">
-        <v>勇气</v>
+        <v>n./vt.</v>
       </c>
       <c r="D15" t="str">
-        <v>courage(勇气)📢</v>
+        <v>男人</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>statue</v>
       </c>
       <c r="B16" t="str">
-        <v>man</v>
+        <v>/ˈstætʃuː/</v>
       </c>
       <c r="C16" t="str">
-        <v>男人</v>
+        <v>n./vt.</v>
       </c>
       <c r="D16" t="str">
-        <v>man(男人)📢</v>
+        <v>雕像</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>double</v>
       </c>
       <c r="B17" t="str">
-        <v>statue</v>
+        <v>/ˈdʌbl/</v>
       </c>
       <c r="C17" t="str">
-        <v>雕像</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D17" t="str">
-        <v>statue(雕像)📢</v>
+        <v>双重的</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>Mediterranean</v>
       </c>
       <c r="B18" t="str">
-        <v>double</v>
+        <v>/ˌmedɪtəˈreɪniən/</v>
       </c>
       <c r="C18" t="str">
-        <v>双重的</v>
+        <v>n./adj.</v>
       </c>
       <c r="D18" t="str">
-        <v>double(双重的)📢</v>
+        <v>地中海</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>evolution</v>
       </c>
       <c r="B19" t="str">
-        <v>Mediterranean</v>
+        <v>/ˌevəˈluːʃn/</v>
       </c>
       <c r="C19" t="str">
-        <v>地中海</v>
+        <v>n.</v>
       </c>
       <c r="D19" t="str">
-        <v>Mediterranean(地中海)📢</v>
+        <v>进化</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>gentle</v>
       </c>
       <c r="B20" t="str">
-        <v>evolution</v>
+        <v>/ˈdʒentl/</v>
       </c>
       <c r="C20" t="str">
-        <v>进化</v>
+        <v>n./vt./adj.</v>
       </c>
       <c r="D20" t="str">
-        <v>evolution(进化)📢</v>
+        <v>温和的</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>elevator</v>
       </c>
       <c r="B21" t="str">
-        <v>Japan</v>
+        <v>/ˈelɪveɪtər/</v>
       </c>
       <c r="C21" t="str">
-        <v>日本</v>
+        <v>n.</v>
       </c>
       <c r="D21" t="str">
-        <v>Japan(日本)📢</v>
+        <v>电梯</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>artificial</v>
       </c>
       <c r="B22" t="str">
-        <v>gentle</v>
+        <v>/ˌɑːrtɪˈfɪʃl/</v>
       </c>
       <c r="C22" t="str">
-        <v>温和的</v>
+        <v>adj.</v>
       </c>
       <c r="D22" t="str">
-        <v>gentle(温和的)📢</v>
+        <v>人造的</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>excite</v>
       </c>
       <c r="B23" t="str">
-        <v>elevator</v>
+        <v>/ɪkˈsaɪt/</v>
       </c>
       <c r="C23" t="str">
-        <v>电梯</v>
+        <v>v.</v>
       </c>
       <c r="D23" t="str">
-        <v>elevator(电梯)📢</v>
+        <v>兴奋</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>alter</v>
       </c>
       <c r="B24" t="str">
-        <v>lately</v>
+        <v>/ˈɔːltər/</v>
       </c>
       <c r="C24" t="str">
-        <v>近来</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D24" t="str">
-        <v>lately(近来)📢</v>
+        <v>改变</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>butter</v>
       </c>
       <c r="B25" t="str">
-        <v>artificial</v>
+        <v>/ˈbʌtər/</v>
       </c>
       <c r="C25" t="str">
-        <v>人造的</v>
+        <v>n./v.</v>
       </c>
       <c r="D25" t="str">
-        <v>artificial(人造的)📢</v>
+        <v>黄油</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>glove</v>
       </c>
       <c r="B26" t="str">
-        <v>excite</v>
+        <v>/ɡlʌv/</v>
       </c>
       <c r="C26" t="str">
-        <v>兴奋</v>
+        <v>n./vt.</v>
       </c>
       <c r="D26" t="str">
-        <v>excite(兴奋)📢</v>
+        <v>手套</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>roller</v>
       </c>
       <c r="B27" t="str">
-        <v>alter</v>
+        <v>/ˈroʊlər/</v>
       </c>
       <c r="C27" t="str">
-        <v>改变</v>
+        <v>n.</v>
       </c>
       <c r="D27" t="str">
-        <v>alter(改变)📢</v>
+        <v>滚筒</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>supply</v>
       </c>
       <c r="B28" t="str">
-        <v>sweet</v>
+        <v>/səˈplaɪ/</v>
       </c>
       <c r="C28" t="str">
-        <v>甜的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D28" t="str">
-        <v>sweet(甜的)📢</v>
+        <v>供应</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>utility</v>
       </c>
       <c r="B29" t="str">
-        <v>butter</v>
+        <v>/juːˈtɪləti/</v>
       </c>
       <c r="C29" t="str">
-        <v>黄油</v>
+        <v>n./adj.</v>
       </c>
       <c r="D29" t="str">
-        <v>butter(黄油)📢</v>
+        <v>实用</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>racket</v>
       </c>
       <c r="B30" t="str">
-        <v>glove</v>
+        <v>/ˈrækɪt/</v>
       </c>
       <c r="C30" t="str">
-        <v>手套</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D30" t="str">
-        <v>glove(手套)📢</v>
+        <v>球拍</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>bang</v>
       </c>
       <c r="B31" t="str">
-        <v>roller</v>
+        <v>/bæŋ/</v>
       </c>
       <c r="C31" t="str">
-        <v>滚筒</v>
+        <v>n./vt./v./adv.</v>
       </c>
       <c r="D31" t="str">
-        <v>roller(滚筒)📢</v>
+        <v>巨响</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>flame</v>
       </c>
       <c r="B32" t="str">
-        <v>supply</v>
+        <v>/fleɪm/</v>
       </c>
       <c r="C32" t="str">
-        <v>供应</v>
+        <v>n./v.</v>
       </c>
       <c r="D32" t="str">
-        <v>supply(供应)📢</v>
+        <v>火焰</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>tone</v>
       </c>
       <c r="B33" t="str">
-        <v>utility</v>
+        <v>/toʊn/</v>
       </c>
       <c r="C33" t="str">
-        <v>实用</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D33" t="str">
-        <v>utility(实用)📢</v>
+        <v>音调</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>desirable</v>
       </c>
       <c r="B34" t="str">
-        <v>racket</v>
+        <v>/dɪˈzaɪərəbl/</v>
       </c>
       <c r="C34" t="str">
-        <v>球拍</v>
+        <v>n./adj.</v>
       </c>
       <c r="D34" t="str">
-        <v>racket(球拍)📢</v>
+        <v>值得拥有的</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>fruit</v>
       </c>
       <c r="B35" t="str">
-        <v>bang</v>
+        <v>/fruːt/</v>
       </c>
       <c r="C35" t="str">
-        <v>巨响</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D35" t="str">
-        <v>bang(巨响)📢</v>
+        <v>水果</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>pork</v>
       </c>
       <c r="B36" t="str">
-        <v>flame</v>
+        <v>/pɔːrk/</v>
       </c>
       <c r="C36" t="str">
-        <v>火焰</v>
+        <v>n./vt.</v>
       </c>
       <c r="D36" t="str">
-        <v>flame(火焰)📢</v>
+        <v>猪肉</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>evident</v>
       </c>
       <c r="B37" t="str">
-        <v>tone</v>
+        <v>/ˈevɪdənt/</v>
       </c>
       <c r="C37" t="str">
-        <v>音调</v>
+        <v>adj.</v>
       </c>
       <c r="D37" t="str">
-        <v>tone(音调)📢</v>
+        <v>明显</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>state</v>
       </c>
       <c r="B38" t="str">
-        <v>desirable</v>
+        <v>/steɪt/</v>
       </c>
       <c r="C38" t="str">
-        <v>值得拥有的</v>
+        <v>n./vt./adj.</v>
       </c>
       <c r="D38" t="str">
-        <v>desirable(值得拥有的)📢</v>
+        <v>国家</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>disadvantage</v>
       </c>
       <c r="B39" t="str">
-        <v>fruit</v>
+        <v>/ˌdɪsədˈvæntɪdʒ/</v>
       </c>
       <c r="C39" t="str">
-        <v>水果</v>
+        <v>n.</v>
       </c>
       <c r="D39" t="str">
-        <v>fruit(水果)📢</v>
+        <v>不利条件</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>because</v>
       </c>
       <c r="B40" t="str">
-        <v>pork</v>
+        <v>/bɪˈkəz,bɪˈkɔːz/</v>
       </c>
       <c r="C40" t="str">
-        <v>猪肉</v>
+        <v>prep./conj.</v>
       </c>
       <c r="D40" t="str">
-        <v>pork(猪肉)📢</v>
+        <v>因为</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>tuck</v>
       </c>
       <c r="B41" t="str">
-        <v>evident</v>
+        <v>/tʌk/</v>
       </c>
       <c r="C41" t="str">
-        <v>明显</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D41" t="str">
-        <v>evident(明显)📢</v>
+        <v>塞进</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>inhabit</v>
       </c>
       <c r="B42" t="str">
-        <v>state</v>
+        <v>/ɪnˈhæbɪt/</v>
       </c>
       <c r="C42" t="str">
-        <v>国家</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D42" t="str">
-        <v>state(国家)📢</v>
+        <v>居住</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>stale</v>
       </c>
       <c r="B43" t="str">
-        <v>disadvantage</v>
+        <v>/steɪl/</v>
       </c>
       <c r="C43" t="str">
-        <v>不利条件</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D43" t="str">
-        <v>disadvantage(不利条件)📢</v>
+        <v>陈腐</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>degree</v>
       </c>
       <c r="B44" t="str">
-        <v>because</v>
+        <v>/dɪˈɡriː/</v>
       </c>
       <c r="C44" t="str">
-        <v>因为</v>
+        <v>n.</v>
       </c>
       <c r="D44" t="str">
-        <v>because(因为)📢</v>
+        <v>程度</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>worm</v>
       </c>
       <c r="B45" t="str">
-        <v>desirable</v>
+        <v>/wɜːrm/</v>
       </c>
       <c r="C45" t="str">
-        <v>值得拥有的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D45" t="str">
-        <v>desirable(值得拥有的)📢</v>
+        <v>虫</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>shilling</v>
       </c>
       <c r="B46" t="str">
-        <v>tuck</v>
+        <v>/ˈʃɪlɪŋ/</v>
       </c>
       <c r="C46" t="str">
-        <v>塞进</v>
+        <v>n.</v>
       </c>
       <c r="D46" t="str">
-        <v>tuck(塞进)📢</v>
+        <v>先令</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>anyway</v>
       </c>
       <c r="B47" t="str">
-        <v>inhabit</v>
+        <v>/ˈeniweɪ/</v>
       </c>
       <c r="C47" t="str">
-        <v>居住</v>
+        <v>v./adv.</v>
       </c>
       <c r="D47" t="str">
-        <v>inhabit(居住)📢</v>
+        <v>无论如何</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>thumb</v>
       </c>
       <c r="B48" t="str">
-        <v>stale</v>
+        <v>/θʌm/</v>
       </c>
       <c r="C48" t="str">
-        <v>陈腐</v>
+        <v>n./v.</v>
       </c>
       <c r="D48" t="str">
-        <v>stale(陈腐)📢</v>
+        <v>拇指</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>tan</v>
       </c>
       <c r="B49" t="str">
-        <v>evolution</v>
+        <v>/tæn/</v>
       </c>
       <c r="C49" t="str">
-        <v>进化</v>
+        <v>n./v./adj.</v>
       </c>
       <c r="D49" t="str">
-        <v>evolution(进化)📢</v>
+        <v>棕褐色</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>before</v>
       </c>
       <c r="B50" t="str">
-        <v>degree</v>
+        <v>/bɪˈfɔːr/</v>
       </c>
       <c r="C50" t="str">
-        <v>程度</v>
+        <v>v./adv./prep./conj.</v>
       </c>
       <c r="D50" t="str">
-        <v>degree(程度)📢</v>
+        <v>在...之前</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>useless</v>
       </c>
       <c r="B51" t="str">
-        <v>worm</v>
+        <v>/ˈjuːsləs/</v>
       </c>
       <c r="C51" t="str">
-        <v>虫</v>
+        <v>adj.</v>
       </c>
       <c r="D51" t="str">
-        <v>worm(虫)📢</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>shilling</v>
-      </c>
-      <c r="C52" t="str">
-        <v>先令</v>
-      </c>
-      <c r="D52" t="str">
-        <v>shilling(先令)📢</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>anyway</v>
-      </c>
-      <c r="C53" t="str">
-        <v>无论如何</v>
-      </c>
-      <c r="D53" t="str">
-        <v>anyway(无论如何)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>thumb</v>
-      </c>
-      <c r="C54" t="str">
-        <v>拇指</v>
-      </c>
-      <c r="D54" t="str">
-        <v>thumb(拇指)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>tan</v>
-      </c>
-      <c r="C55" t="str">
-        <v>棕褐色</v>
-      </c>
-      <c r="D55" t="str">
-        <v>tan(棕褐色)📢</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
-        <v>river</v>
-      </c>
-      <c r="C56" t="str">
-        <v>河流</v>
-      </c>
-      <c r="D56" t="str">
-        <v>river(河流)📢</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="str">
-        <v>before</v>
-      </c>
-      <c r="C57" t="str">
-        <v>在...之前</v>
-      </c>
-      <c r="D57" t="str">
-        <v>before(在...之前)📢</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="str">
-        <v>before</v>
-      </c>
-      <c r="C58" t="str">
-        <v>在...之前</v>
-      </c>
-      <c r="D58" t="str">
-        <v>before(在...之前)📢</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59" t="str">
-        <v>bed</v>
-      </c>
-      <c r="C59" t="str">
-        <v>床</v>
-      </c>
-      <c r="D59" t="str">
-        <v>bed(床)📢</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60" t="str">
-        <v>useless</v>
-      </c>
-      <c r="C60" t="str">
         <v>无用的</v>
-      </c>
-      <c r="D60" t="str">
-        <v>useless(无用的)📢</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61">
-        <v>60</v>
-      </c>
-      <c r="B61" t="str">
-        <v>flame</v>
-      </c>
-      <c r="C61" t="str">
-        <v>火焰</v>
-      </c>
-      <c r="D61" t="str">
-        <v>flame(火焰)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D51"/>
   </ignoredErrors>
 </worksheet>
 </file>